--- a/output/yearly_benthic_cover_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_88_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.0475674434918</v>
+        <v>45.20314761362128</v>
       </c>
       <c r="M2" t="n">
-        <v>100.9504790257735</v>
+        <v>101.0971032188988</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93523529140036</v>
+        <v>87.92910918572588</v>
       </c>
       <c r="C3" t="n">
-        <v>45.85712130157154</v>
+        <v>45.83946825066455</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228548524973593</v>
+        <v>2.228546184030364</v>
       </c>
       <c r="E3" t="n">
-        <v>5.660554096642605</v>
+        <v>5.650195650677697</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742849508324531</v>
+        <v>0.7428487280101216</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94922288512276</v>
+        <v>33.94314779061496</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17107738292842</v>
+        <v>34.17104148846559</v>
       </c>
       <c r="I3" t="n">
-        <v>6.540173466380119</v>
+        <v>6.550524793863881</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642809427028319</v>
+        <v>4.64280455006326</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06476470859964</v>
+        <v>12.07089081427414</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84333611918918</v>
+        <v>48.85449122747868</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652221293604</v>
+        <v>106.7648502924174</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.92994462905527</v>
+        <v>86.97601488737371</v>
       </c>
       <c r="C4" t="n">
-        <v>42.48424177860453</v>
+        <v>42.52143916523987</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179555962803339</v>
+        <v>2.182324585598606</v>
       </c>
       <c r="E4" t="n">
-        <v>6.446371832885369</v>
+        <v>6.44470910786946</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744405211608868</v>
+        <v>0.744406070004726</v>
       </c>
       <c r="G4" t="n">
-        <v>33.20288086286372</v>
+        <v>33.23914328851833</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24263973400792</v>
+        <v>34.2426792202174</v>
       </c>
       <c r="I4" t="n">
-        <v>5.461558452330633</v>
+        <v>5.470214677635652</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652532572555425</v>
+        <v>4.652537937529537</v>
       </c>
       <c r="K4" t="n">
-        <v>13.07005537094473</v>
+        <v>13.02398511262629</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26403136527351</v>
+        <v>44.27261670008208</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81832851482277</v>
+        <v>99.81804097794824</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.66487623034638</v>
+        <v>85.78088749871419</v>
       </c>
       <c r="C5" t="n">
-        <v>42.06669525649831</v>
+        <v>42.17520770189209</v>
       </c>
       <c r="D5" t="n">
-        <v>2.117387411540024</v>
+        <v>2.123789174176083</v>
       </c>
       <c r="E5" t="n">
-        <v>7.022394322596784</v>
+        <v>7.032946102672611</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457258700240833</v>
+        <v>0.7457270347356134</v>
       </c>
       <c r="G5" t="n">
-        <v>32.2558186922931</v>
+        <v>32.3475862119197</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30339002110783</v>
+        <v>34.30344359783822</v>
       </c>
       <c r="I5" t="n">
-        <v>4.559373225134032</v>
+        <v>4.566601410274375</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660786687650521</v>
+        <v>4.660793967097583</v>
       </c>
       <c r="K5" t="n">
-        <v>14.33512376965363</v>
+        <v>14.21911250128582</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44647101683887</v>
+        <v>43.45372938910997</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84829004299081</v>
+        <v>99.84804959228788</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.16755964954423</v>
+        <v>84.39071105631261</v>
       </c>
       <c r="C6" t="n">
-        <v>41.27725599692045</v>
+        <v>41.4941222769739</v>
       </c>
       <c r="D6" t="n">
-        <v>2.043875055180728</v>
+        <v>2.055743454235564</v>
       </c>
       <c r="E6" t="n">
-        <v>7.412788431372747</v>
+        <v>7.442817106553573</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468496753989385</v>
+        <v>0.7468496453355511</v>
       </c>
       <c r="G6" t="n">
-        <v>31.13594746540029</v>
+        <v>31.31117693980728</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35508506835117</v>
+        <v>34.35508368543535</v>
       </c>
       <c r="I6" t="n">
-        <v>3.805203482596978</v>
+        <v>3.811229941598101</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667810471243366</v>
+        <v>4.667810283347194</v>
       </c>
       <c r="K6" t="n">
-        <v>15.83244035045578</v>
+        <v>15.60928894368737</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76365439637004</v>
+        <v>42.76973874016445</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87335074374627</v>
+        <v>99.87314996082571</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.45743271075305</v>
+        <v>82.68279288847702</v>
       </c>
       <c r="C7" t="n">
-        <v>40.15783417225555</v>
+        <v>40.37800646998497</v>
       </c>
       <c r="D7" t="n">
-        <v>1.960281436265369</v>
+        <v>1.972234306092389</v>
       </c>
       <c r="E7" t="n">
-        <v>7.638787367564847</v>
+        <v>7.670488447194547</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478082719024149</v>
+        <v>0.7478071416729658</v>
       </c>
       <c r="G7" t="n">
-        <v>29.86250048027568</v>
+        <v>30.03924307655396</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39918050751109</v>
+        <v>34.39912851695643</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17507294784356</v>
+        <v>3.180096764550691</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673801699390093</v>
+        <v>4.673794635456035</v>
       </c>
       <c r="K7" t="n">
-        <v>17.54256728924696</v>
+        <v>17.31720711152299</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19389844175868</v>
+        <v>42.19891892011429</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89429990326119</v>
+        <v>99.89413250162225</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.38173428733862</v>
+        <v>87.51249995423021</v>
       </c>
       <c r="C8" t="n">
-        <v>42.51673772329097</v>
+        <v>42.65531334739629</v>
       </c>
       <c r="D8" t="n">
-        <v>1.964481881274768</v>
+        <v>1.976448376199601</v>
       </c>
       <c r="E8" t="n">
-        <v>9.50875767697821</v>
+        <v>9.485388138968789</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494106578994401</v>
+        <v>0.7494049800798679</v>
       </c>
       <c r="G8" t="n">
-        <v>30.38519137390065</v>
+        <v>30.53521339670782</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47289026337425</v>
+        <v>34.47262908367393</v>
       </c>
       <c r="I8" t="n">
-        <v>5.617185822039791</v>
+        <v>5.609634853101033</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6838166118715</v>
+        <v>4.683781125499173</v>
       </c>
       <c r="K8" t="n">
-        <v>12.61826571266139</v>
+        <v>12.4875000457698</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67815739123647</v>
+        <v>44.6705974631429</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81316082718884</v>
+        <v>99.81341085630898</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.27202791841876</v>
+        <v>85.33375640887667</v>
       </c>
       <c r="C9" t="n">
-        <v>41.27829991863874</v>
+        <v>41.34682729842214</v>
       </c>
       <c r="D9" t="n">
-        <v>1.868889791528668</v>
+        <v>1.87734132612658</v>
       </c>
       <c r="E9" t="n">
-        <v>9.827654465312769</v>
+        <v>9.790293981663147</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507844625277531</v>
+        <v>0.7507759299310585</v>
       </c>
       <c r="G9" t="n">
-        <v>28.90664175302985</v>
+        <v>29.00405530548718</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53608527627664</v>
+        <v>34.5356927768287</v>
       </c>
       <c r="I9" t="n">
-        <v>4.68956927894461</v>
+        <v>4.6832475267709</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692402890798457</v>
+        <v>4.692349562069115</v>
       </c>
       <c r="K9" t="n">
-        <v>14.72797208158124</v>
+        <v>14.66624359112332</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8376950602789</v>
+        <v>43.83110592009063</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8439670604989</v>
+        <v>99.8441768096361</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.02797789150998</v>
+        <v>83.13181742019512</v>
       </c>
       <c r="C10" t="n">
-        <v>39.76124951201035</v>
+        <v>39.87097859991126</v>
       </c>
       <c r="D10" t="n">
-        <v>1.76837477791244</v>
+        <v>1.778486376622568</v>
       </c>
       <c r="E10" t="n">
-        <v>9.951443590281313</v>
+        <v>9.926238090589646</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519642483888506</v>
+        <v>0.7519526355367896</v>
       </c>
       <c r="G10" t="n">
-        <v>27.35194789008752</v>
+        <v>27.47679205147293</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59035542588713</v>
+        <v>34.58982123469233</v>
       </c>
       <c r="I10" t="n">
-        <v>3.914115406522407</v>
+        <v>3.908823059175932</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699776552430316</v>
+        <v>4.699703972104935</v>
       </c>
       <c r="K10" t="n">
-        <v>16.97202210849002</v>
+        <v>16.86818257980487</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13646256619561</v>
+        <v>43.1307486112069</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86973418669598</v>
+        <v>99.86990979092303</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.76085390623302</v>
+        <v>80.86093980011148</v>
       </c>
       <c r="C11" t="n">
-        <v>38.10023366118794</v>
+        <v>38.20548362569048</v>
       </c>
       <c r="D11" t="n">
-        <v>1.668011104973491</v>
+        <v>1.677661807200178</v>
       </c>
       <c r="E11" t="n">
-        <v>9.931011863823313</v>
+        <v>9.907129560421163</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529779554819988</v>
+        <v>0.7529636998129774</v>
       </c>
       <c r="G11" t="n">
-        <v>25.79959485578075</v>
+        <v>25.91909908057747</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63698595217194</v>
+        <v>34.63633019139697</v>
       </c>
       <c r="I11" t="n">
-        <v>3.266159952239042</v>
+        <v>3.261732336871583</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706112221762492</v>
+        <v>4.706023123831109</v>
       </c>
       <c r="K11" t="n">
-        <v>19.23914609376698</v>
+        <v>19.13906019988854</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55189481708612</v>
+        <v>42.54687775611054</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89127457204103</v>
+        <v>99.89142158168956</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.49184731391105</v>
+        <v>78.49793884583289</v>
       </c>
       <c r="C12" t="n">
-        <v>36.33622251443744</v>
+        <v>36.34687157385427</v>
       </c>
       <c r="D12" t="n">
-        <v>1.568624555921797</v>
+        <v>1.573774145421029</v>
       </c>
       <c r="E12" t="n">
-        <v>9.793442066641347</v>
+        <v>9.747181555813421</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538493101056349</v>
+        <v>0.7538337877832942</v>
       </c>
       <c r="G12" t="n">
-        <v>24.26235527026334</v>
+        <v>24.31408274930803</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6770682648592</v>
+        <v>34.67635423803155</v>
       </c>
       <c r="I12" t="n">
-        <v>2.724949657959495</v>
+        <v>2.721251195829985</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711558188160218</v>
+        <v>4.711461173645589</v>
       </c>
       <c r="K12" t="n">
-        <v>21.50815268608897</v>
+        <v>21.50206115416711</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06489813413363</v>
+        <v>42.0604635959544</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90927333466003</v>
+        <v>99.90939632397578</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.15066609487363</v>
+        <v>76.08699437982342</v>
       </c>
       <c r="C13" t="n">
-        <v>34.41555521416685</v>
+        <v>34.35587932729268</v>
       </c>
       <c r="D13" t="n">
-        <v>1.466995185989638</v>
+        <v>1.468757154462089</v>
       </c>
       <c r="E13" t="n">
-        <v>9.537778082531004</v>
+        <v>9.475085475248473</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545993747886853</v>
+        <v>0.7545834454321082</v>
       </c>
       <c r="G13" t="n">
-        <v>22.69042534612796</v>
+        <v>22.69161880447312</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71157124027953</v>
+        <v>34.71083848987699</v>
       </c>
       <c r="I13" t="n">
-        <v>2.273050772727533</v>
+        <v>2.269964476379962</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716246092429284</v>
+        <v>4.716146533950676</v>
       </c>
       <c r="K13" t="n">
-        <v>23.84933390512639</v>
+        <v>23.91300562017658</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65941783465233</v>
+        <v>41.65552474153546</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92430695394556</v>
+        <v>99.92440968900473</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.20836398114932</v>
+        <v>82.99096576952088</v>
       </c>
       <c r="C14" t="n">
-        <v>38.86807398626536</v>
+        <v>38.77684072307565</v>
       </c>
       <c r="D14" t="n">
-        <v>1.468669404031292</v>
+        <v>1.470369572395723</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99772757837528</v>
+        <v>11.90906420004382</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554605663587449</v>
+        <v>0.7554118355278715</v>
       </c>
       <c r="G14" t="n">
-        <v>24.69057488620774</v>
+        <v>24.68456476197028</v>
       </c>
       <c r="H14" t="n">
-        <v>36.72543999329849</v>
+        <v>36.71697928037303</v>
       </c>
       <c r="I14" t="n">
-        <v>2.848863013135614</v>
+        <v>2.733252147160962</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721628539742156</v>
+        <v>4.721323972049197</v>
       </c>
       <c r="K14" t="n">
-        <v>16.79163601885068</v>
+        <v>17.0090342304791</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24543614703271</v>
+        <v>44.12311655167726</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90514615214875</v>
+        <v>99.90899150523202</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.58357974216666</v>
+        <v>82.20103193172983</v>
       </c>
       <c r="C15" t="n">
-        <v>38.67674263237064</v>
+        <v>38.40909488591898</v>
       </c>
       <c r="D15" t="n">
-        <v>1.445246321257213</v>
+        <v>1.441186443047309</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20902397777385</v>
+        <v>12.05266860366141</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561851750194902</v>
+        <v>0.7561102046466361</v>
       </c>
       <c r="G15" t="n">
-        <v>24.30338439929974</v>
+        <v>24.19463837891535</v>
       </c>
       <c r="H15" t="n">
-        <v>36.76725291432273</v>
+        <v>36.75092368428327</v>
       </c>
       <c r="I15" t="n">
-        <v>2.376329610621828</v>
+        <v>2.279815838134388</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726157343871814</v>
+        <v>4.725688779041476</v>
       </c>
       <c r="K15" t="n">
-        <v>17.41642025783335</v>
+        <v>17.79896806827016</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82770202609779</v>
+        <v>43.71601337505636</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92086491630178</v>
+        <v>99.92407632924551</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.2131891801709</v>
+        <v>79.7479291256513</v>
       </c>
       <c r="C16" t="n">
-        <v>36.67349509060757</v>
+        <v>36.30814191282194</v>
       </c>
       <c r="D16" t="n">
-        <v>1.356109133718088</v>
+        <v>1.348452006404597</v>
       </c>
       <c r="E16" t="n">
-        <v>11.78633633764794</v>
+        <v>11.59402154723324</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568079685482785</v>
+        <v>0.7567111126152913</v>
       </c>
       <c r="G16" t="n">
-        <v>22.80444591305518</v>
+        <v>22.63781263255408</v>
       </c>
       <c r="H16" t="n">
-        <v>36.79753439555617</v>
+        <v>36.78013096486434</v>
       </c>
       <c r="I16" t="n">
-        <v>1.981905628218505</v>
+        <v>1.901356408134182</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73004980342674</v>
+        <v>4.729444453845571</v>
       </c>
       <c r="K16" t="n">
-        <v>19.78681081982911</v>
+        <v>20.25207087434871</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47368493371273</v>
+        <v>43.37645899510341</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93399084414941</v>
+        <v>99.93667178227406</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.08607909303959</v>
+        <v>81.46854996959129</v>
       </c>
       <c r="C17" t="n">
-        <v>38.0397091476552</v>
+        <v>37.5746855024472</v>
       </c>
       <c r="D17" t="n">
-        <v>1.357182823895346</v>
+        <v>1.349478095736248</v>
       </c>
       <c r="E17" t="n">
-        <v>12.62667961106014</v>
+        <v>12.37714032480852</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574071661067175</v>
+        <v>0.7572869233939536</v>
       </c>
       <c r="G17" t="n">
-        <v>23.32855722742124</v>
+        <v>23.11937219126241</v>
       </c>
       <c r="H17" t="n">
-        <v>37.33272464249455</v>
+        <v>37.27245196105557</v>
       </c>
       <c r="I17" t="n">
-        <v>1.949732833894602</v>
+        <v>1.859777202122393</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733794788166985</v>
+        <v>4.73304327121221</v>
       </c>
       <c r="K17" t="n">
-        <v>17.91392090696042</v>
+        <v>18.53145003040871</v>
       </c>
       <c r="L17" t="n">
-        <v>43.98143026647005</v>
+        <v>43.83191903042079</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93506032108567</v>
+        <v>99.93805456327669</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.77657652366121</v>
+        <v>79.06285576015081</v>
       </c>
       <c r="C18" t="n">
-        <v>36.03112048603488</v>
+        <v>35.45588571494433</v>
       </c>
       <c r="D18" t="n">
-        <v>1.274043092174747</v>
+        <v>1.262194688232923</v>
       </c>
       <c r="E18" t="n">
-        <v>12.12416139351916</v>
+        <v>11.83506583069356</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579217089663887</v>
+        <v>0.7577820659390353</v>
       </c>
       <c r="G18" t="n">
-        <v>21.89947195227042</v>
+        <v>21.62402551570926</v>
       </c>
       <c r="H18" t="n">
-        <v>37.358086545255</v>
+        <v>37.29682208571415</v>
       </c>
       <c r="I18" t="n">
-        <v>1.625881150435565</v>
+        <v>1.550827661742902</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737010681039929</v>
+        <v>4.736137912118971</v>
       </c>
       <c r="K18" t="n">
-        <v>20.22342347633879</v>
+        <v>20.93714423984918</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69129679224037</v>
+        <v>43.55530956736977</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94584075461404</v>
+        <v>99.94833952216328</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.8719941889682</v>
+        <v>78.12158551375008</v>
       </c>
       <c r="C19" t="n">
-        <v>35.37683263868709</v>
+        <v>34.74971601622175</v>
       </c>
       <c r="D19" t="n">
-        <v>1.242104121607084</v>
+        <v>1.228509974814146</v>
       </c>
       <c r="E19" t="n">
-        <v>12.04616714790759</v>
+        <v>11.73529112158604</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758355955715186</v>
+        <v>0.7582012482767118</v>
       </c>
       <c r="G19" t="n">
-        <v>21.35047435993859</v>
+        <v>21.04693617343295</v>
       </c>
       <c r="H19" t="n">
-        <v>37.3794906394136</v>
+        <v>37.31745357037514</v>
       </c>
       <c r="I19" t="n">
-        <v>1.355677241166242</v>
+        <v>1.29643562353565</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739724723219912</v>
+        <v>4.738757801729449</v>
       </c>
       <c r="K19" t="n">
-        <v>21.1280058110318</v>
+        <v>21.87841448624989</v>
       </c>
       <c r="L19" t="n">
-        <v>43.44999818499123</v>
+        <v>43.32867886850592</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95483663471012</v>
+        <v>99.95680937097758</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.38723001942768</v>
+        <v>75.46689063408152</v>
       </c>
       <c r="C20" t="n">
-        <v>33.10062592134548</v>
+        <v>32.2943041417101</v>
       </c>
       <c r="D20" t="n">
-        <v>1.153572133739293</v>
+        <v>1.133159839549335</v>
       </c>
       <c r="E20" t="n">
-        <v>11.37594810002163</v>
+        <v>11.00460933472631</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587299976524695</v>
+        <v>0.7585632276172635</v>
       </c>
       <c r="G20" t="n">
-        <v>19.82870182563605</v>
+        <v>19.41338963967342</v>
       </c>
       <c r="H20" t="n">
-        <v>37.3979272284429</v>
+        <v>37.33526961494798</v>
       </c>
       <c r="I20" t="n">
-        <v>1.130288248607399</v>
+        <v>1.080878804959326</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742062485327934</v>
+        <v>4.741020172607898</v>
       </c>
       <c r="K20" t="n">
-        <v>23.61276998057231</v>
+        <v>24.53310936591848</v>
       </c>
       <c r="L20" t="n">
-        <v>43.24894639693872</v>
+        <v>43.13657439171763</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96234229885651</v>
+        <v>99.96398789934621</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.25779658398939</v>
+        <v>81.3084367365057</v>
       </c>
       <c r="C21" t="n">
-        <v>36.77368111501416</v>
+        <v>36.01096844290389</v>
       </c>
       <c r="D21" t="n">
-        <v>1.154318469937904</v>
+        <v>1.133830440564298</v>
       </c>
       <c r="E21" t="n">
-        <v>13.34590306772648</v>
+        <v>12.98313552615466</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592208795363655</v>
+        <v>0.7590121433417703</v>
       </c>
       <c r="G21" t="n">
-        <v>21.53803047343764</v>
+        <v>21.15630152932643</v>
       </c>
       <c r="H21" t="n">
-        <v>39.11862278475082</v>
+        <v>39.08878762606946</v>
       </c>
       <c r="I21" t="n">
-        <v>1.596570411497887</v>
+        <v>1.443543575163014</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745130497102284</v>
+        <v>4.743825895886065</v>
       </c>
       <c r="K21" t="n">
-        <v>17.74220341601061</v>
+        <v>18.69156326349432</v>
       </c>
       <c r="L21" t="n">
-        <v>45.43093086454636</v>
+        <v>45.24937863376399</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94681539557114</v>
+        <v>99.95191034016219</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_88_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.20314761362128</v>
+        <v>45.25906449791488</v>
       </c>
       <c r="M2" t="n">
-        <v>101.0971032188988</v>
+        <v>100.022290745528</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92910918572588</v>
+        <v>87.98673777596514</v>
       </c>
       <c r="C3" t="n">
-        <v>45.83946825066455</v>
+        <v>45.90305264062242</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228546184030364</v>
+        <v>2.228645944559007</v>
       </c>
       <c r="E3" t="n">
-        <v>5.650195650677697</v>
+        <v>5.689514319665689</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428487280101216</v>
+        <v>0.7428819815196692</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94314779061496</v>
+        <v>33.96464613358971</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17104148846559</v>
+        <v>34.17257114990478</v>
       </c>
       <c r="I3" t="n">
-        <v>6.550524793863881</v>
+        <v>6.545465862228343</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64280455006326</v>
+        <v>4.643012384497932</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07089081427414</v>
+        <v>12.01326222403485</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85449122747868</v>
+        <v>48.84872755033167</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648502924174</v>
+        <v>106.765042414989</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.97601488737371</v>
+        <v>87.01679290937517</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52143916523987</v>
+        <v>42.56483599360912</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182324585598606</v>
+        <v>2.18159210580652</v>
       </c>
       <c r="E4" t="n">
-        <v>6.44470910786946</v>
+        <v>6.48038646298469</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744406070004726</v>
+        <v>0.7444374571287393</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23914328851833</v>
+        <v>33.24754390101798</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2426792202174</v>
+        <v>34.244123027922</v>
       </c>
       <c r="I4" t="n">
-        <v>5.470214677635652</v>
+        <v>5.46597584746062</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652537937529537</v>
+        <v>4.65273410705462</v>
       </c>
       <c r="K4" t="n">
-        <v>13.02398511262629</v>
+        <v>12.98320709062486</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27261670008208</v>
+        <v>44.27013841959299</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81804097794824</v>
+        <v>99.81818150382696</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.78088749871419</v>
+        <v>85.86511992243439</v>
       </c>
       <c r="C5" t="n">
-        <v>42.17520770189209</v>
+        <v>42.26145025214448</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123789174176083</v>
+        <v>2.125400270905126</v>
       </c>
       <c r="E5" t="n">
-        <v>7.032946102672611</v>
+        <v>7.073977559823236</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457270347356134</v>
+        <v>0.7457561549029267</v>
       </c>
       <c r="G5" t="n">
-        <v>32.3475862119197</v>
+        <v>32.39117827116887</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30344359783822</v>
+        <v>34.30478312553462</v>
       </c>
       <c r="I5" t="n">
-        <v>4.566601410274375</v>
+        <v>4.563048571956312</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660793967097583</v>
+        <v>4.660975968143291</v>
       </c>
       <c r="K5" t="n">
-        <v>14.21911250128582</v>
+        <v>14.13488007756562</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45372938910997</v>
+        <v>43.45183700786047</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84804959228788</v>
+        <v>99.84816733757056</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.39071105631261</v>
+        <v>84.48550194050144</v>
       </c>
       <c r="C6" t="n">
-        <v>41.4941222769739</v>
+        <v>41.59045102097226</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055743454235564</v>
+        <v>2.057985257272667</v>
       </c>
       <c r="E6" t="n">
-        <v>7.442817106553573</v>
+        <v>7.484308904427374</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468496453355511</v>
+        <v>0.7468766740922376</v>
       </c>
       <c r="G6" t="n">
-        <v>31.31117693980728</v>
+        <v>31.36377098482637</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35508368543535</v>
+        <v>34.35632700824292</v>
       </c>
       <c r="I6" t="n">
-        <v>3.811229941598101</v>
+        <v>3.808253898563398</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667810283347194</v>
+        <v>4.667979213076484</v>
       </c>
       <c r="K6" t="n">
-        <v>15.60928894368737</v>
+        <v>15.51449805949855</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76973874016445</v>
+        <v>42.76829957030817</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87314996082571</v>
+        <v>99.87324865077898</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.68279288847702</v>
+        <v>82.83125322206455</v>
       </c>
       <c r="C7" t="n">
-        <v>40.37800646998497</v>
+        <v>40.52761725476002</v>
       </c>
       <c r="D7" t="n">
-        <v>1.972234306092389</v>
+        <v>1.977285174616775</v>
       </c>
       <c r="E7" t="n">
-        <v>7.670488447194547</v>
+        <v>7.720426095772588</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478071416729658</v>
+        <v>0.7478317393692447</v>
       </c>
       <c r="G7" t="n">
-        <v>30.03924307655396</v>
+        <v>30.13389875812722</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39912851695643</v>
+        <v>34.40026001098525</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180096764550691</v>
+        <v>3.177603072135687</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673794635456035</v>
+        <v>4.673948371057779</v>
       </c>
       <c r="K7" t="n">
-        <v>17.31720711152299</v>
+        <v>17.16874677793543</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19891892011429</v>
+        <v>42.19785113678891</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89413250162225</v>
+        <v>99.89421516948437</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.51249995423021</v>
+        <v>87.80202852384625</v>
       </c>
       <c r="C8" t="n">
-        <v>42.65531334739629</v>
+        <v>42.86634089345949</v>
       </c>
       <c r="D8" t="n">
-        <v>1.976448376199601</v>
+        <v>1.981552409529754</v>
       </c>
       <c r="E8" t="n">
-        <v>9.485388138968789</v>
+        <v>9.580790854146526</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494049800798679</v>
+        <v>0.7494456561417144</v>
       </c>
       <c r="G8" t="n">
-        <v>30.53521339670782</v>
+        <v>30.64706303314896</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47262908367393</v>
+        <v>34.47450018251886</v>
       </c>
       <c r="I8" t="n">
-        <v>5.609634853101033</v>
+        <v>5.684641037474714</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683781125499173</v>
+        <v>4.684035350885715</v>
       </c>
       <c r="K8" t="n">
-        <v>12.4875000457698</v>
+        <v>12.19797147615376</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6705974631429</v>
+        <v>44.74660765463371</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81341085630898</v>
+        <v>99.81092002424695</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.33375640887667</v>
+        <v>85.79586632378928</v>
       </c>
       <c r="C9" t="n">
-        <v>41.34682729842214</v>
+        <v>41.74222323033705</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87734132612658</v>
+        <v>1.890851711591879</v>
       </c>
       <c r="E9" t="n">
-        <v>9.790293981663147</v>
+        <v>9.933242956019249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507759299310585</v>
+        <v>0.7508275490256746</v>
       </c>
       <c r="G9" t="n">
-        <v>29.00405530548718</v>
+        <v>29.24426894428996</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5356927768287</v>
+        <v>34.53806725518103</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6832475267709</v>
+        <v>4.745935726271021</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692349562069115</v>
+        <v>4.692672181410466</v>
       </c>
       <c r="K9" t="n">
-        <v>14.66624359112332</v>
+        <v>14.20413367621072</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83110592009063</v>
+        <v>43.89573639796684</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8441768096361</v>
+        <v>99.84209330451461</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.13181742019512</v>
+        <v>83.69839117098132</v>
       </c>
       <c r="C10" t="n">
-        <v>39.87097859991126</v>
+        <v>40.38087374787868</v>
       </c>
       <c r="D10" t="n">
-        <v>1.778486376622568</v>
+        <v>1.797111265649347</v>
       </c>
       <c r="E10" t="n">
-        <v>9.926238090589646</v>
+        <v>10.10099230470523</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519526355367896</v>
+        <v>0.7520120271049393</v>
       </c>
       <c r="G10" t="n">
-        <v>27.47679205147293</v>
+        <v>27.79446153988321</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58982123469233</v>
+        <v>34.5925532468272</v>
       </c>
       <c r="I10" t="n">
-        <v>3.908823059175932</v>
+        <v>3.961185617405537</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699703972104935</v>
+        <v>4.700075169405871</v>
       </c>
       <c r="K10" t="n">
-        <v>16.86818257980487</v>
+        <v>16.30160882901866</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1307486112069</v>
+        <v>43.18568587515067</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86990979092303</v>
+        <v>99.86816845204801</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.86093980011148</v>
+        <v>81.45097777008448</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20548362569048</v>
+        <v>38.74732840552995</v>
       </c>
       <c r="D11" t="n">
-        <v>1.677661807200178</v>
+        <v>1.697651277727326</v>
       </c>
       <c r="E11" t="n">
-        <v>9.907129560421163</v>
+        <v>10.09286816287799</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529636998129774</v>
+        <v>0.753029301858441</v>
       </c>
       <c r="G11" t="n">
-        <v>25.91909908057747</v>
+        <v>26.25619462124754</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63633019139697</v>
+        <v>34.63934788548828</v>
       </c>
       <c r="I11" t="n">
-        <v>3.261732336871583</v>
+        <v>3.305453384269636</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706023123831109</v>
+        <v>4.706433136615257</v>
       </c>
       <c r="K11" t="n">
-        <v>19.13906019988854</v>
+        <v>18.54902222991554</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54687775611054</v>
+        <v>42.59361643073768</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89142158168956</v>
+        <v>99.88996706618316</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.49793884583289</v>
+        <v>79.14553095628763</v>
       </c>
       <c r="C12" t="n">
-        <v>36.34687157385427</v>
+        <v>36.95338729772971</v>
       </c>
       <c r="D12" t="n">
-        <v>1.573774145421029</v>
+        <v>1.596634106869513</v>
       </c>
       <c r="E12" t="n">
-        <v>9.747181555813421</v>
+        <v>9.95192533324801</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538337877832942</v>
+        <v>0.7539039193129358</v>
       </c>
       <c r="G12" t="n">
-        <v>24.31408274930803</v>
+        <v>24.69384401784135</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67635423803155</v>
+        <v>34.67958028839504</v>
       </c>
       <c r="I12" t="n">
-        <v>2.721251195829985</v>
+        <v>2.757743794914931</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711461173645589</v>
+        <v>4.711899495705849</v>
       </c>
       <c r="K12" t="n">
-        <v>21.50206115416711</v>
+        <v>20.85446904371237</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0604635959544</v>
+        <v>42.1003255089949</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90939632397578</v>
+        <v>99.90818185043697</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.08699437982342</v>
+        <v>76.91311236069588</v>
       </c>
       <c r="C13" t="n">
-        <v>34.35587932729268</v>
+        <v>35.14690875319604</v>
       </c>
       <c r="D13" t="n">
-        <v>1.468757154462089</v>
+        <v>1.499780196671745</v>
       </c>
       <c r="E13" t="n">
-        <v>9.475085475248473</v>
+        <v>9.731630377311857</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545834454321082</v>
+        <v>0.7546555418523776</v>
       </c>
       <c r="G13" t="n">
-        <v>22.69161880447312</v>
+        <v>23.19588318846196</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71083848987699</v>
+        <v>34.71415492520936</v>
       </c>
       <c r="I13" t="n">
-        <v>2.269964476379962</v>
+        <v>2.300410994611218</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716146533950676</v>
+        <v>4.71659713657736</v>
       </c>
       <c r="K13" t="n">
-        <v>23.91300562017658</v>
+        <v>23.0868876393041</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65552474153546</v>
+        <v>41.68959961319666</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92440968900473</v>
+        <v>99.92339600569682</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.99096576952088</v>
+        <v>83.62462500774997</v>
       </c>
       <c r="C14" t="n">
-        <v>38.77684072307565</v>
+        <v>39.38496107538261</v>
       </c>
       <c r="D14" t="n">
-        <v>1.470369572395723</v>
+        <v>1.501485868948057</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90906420004382</v>
+        <v>12.08435571790041</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554118355278715</v>
+        <v>0.7555137976412986</v>
       </c>
       <c r="G14" t="n">
-        <v>24.68456476197028</v>
+        <v>25.08839747862212</v>
       </c>
       <c r="H14" t="n">
-        <v>36.71697928037303</v>
+        <v>36.61976873276281</v>
       </c>
       <c r="I14" t="n">
-        <v>2.733252147160962</v>
+        <v>2.853142176617161</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721323972049197</v>
+        <v>4.721961235258116</v>
       </c>
       <c r="K14" t="n">
-        <v>17.0090342304791</v>
+        <v>16.37537499225003</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12311655167726</v>
+        <v>44.14466723113793</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90899150523202</v>
+        <v>99.90500329877057</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.20103193172983</v>
+        <v>83.00616322398264</v>
       </c>
       <c r="C15" t="n">
-        <v>38.40909488591898</v>
+        <v>39.20756082609695</v>
       </c>
       <c r="D15" t="n">
-        <v>1.441186443047309</v>
+        <v>1.478886788379759</v>
       </c>
       <c r="E15" t="n">
-        <v>12.05266860366141</v>
+        <v>12.29912080059524</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561102046466361</v>
+        <v>0.7562358485747722</v>
       </c>
       <c r="G15" t="n">
-        <v>24.19463837891535</v>
+        <v>24.71078838640597</v>
       </c>
       <c r="H15" t="n">
-        <v>36.75092368428327</v>
+        <v>36.65476655580672</v>
       </c>
       <c r="I15" t="n">
-        <v>2.279815838134388</v>
+        <v>2.379890790627841</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725688779041476</v>
+        <v>4.726474053592327</v>
       </c>
       <c r="K15" t="n">
-        <v>17.79896806827016</v>
+        <v>16.99383677601735</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71601337505636</v>
+        <v>43.71934844853522</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92407632924551</v>
+        <v>99.92074605064954</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.7479291256513</v>
+        <v>80.64436295439906</v>
       </c>
       <c r="C16" t="n">
-        <v>36.30814191282194</v>
+        <v>37.21377194195935</v>
       </c>
       <c r="D16" t="n">
-        <v>1.348452006404597</v>
+        <v>1.38927624326295</v>
       </c>
       <c r="E16" t="n">
-        <v>11.59402154723324</v>
+        <v>11.88468876685721</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567111126152913</v>
+        <v>0.7568562802058053</v>
       </c>
       <c r="G16" t="n">
-        <v>22.63781263255408</v>
+        <v>23.21348160473003</v>
       </c>
       <c r="H16" t="n">
-        <v>36.78013096486434</v>
+        <v>36.68483888924901</v>
       </c>
       <c r="I16" t="n">
-        <v>1.901356408134182</v>
+        <v>1.984869418807759</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729444453845571</v>
+        <v>4.730351751286283</v>
       </c>
       <c r="K16" t="n">
-        <v>20.25207087434871</v>
+        <v>19.35563704560095</v>
       </c>
       <c r="L16" t="n">
-        <v>43.37645899510341</v>
+        <v>43.36448293492224</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93667178227406</v>
+        <v>99.93389192248254</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.46854996959129</v>
+        <v>82.41521001088832</v>
       </c>
       <c r="C17" t="n">
-        <v>37.5746855024472</v>
+        <v>38.50778374539037</v>
       </c>
       <c r="D17" t="n">
-        <v>1.349478095736248</v>
+        <v>1.39037755196683</v>
       </c>
       <c r="E17" t="n">
-        <v>12.37714032480852</v>
+        <v>12.6896819370207</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572869233939536</v>
+        <v>0.7574562562098716</v>
       </c>
       <c r="G17" t="n">
-        <v>23.11937219126241</v>
+        <v>23.70079393598982</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27245196105557</v>
+        <v>37.18283025076104</v>
       </c>
       <c r="I17" t="n">
-        <v>1.859777202122393</v>
+        <v>1.959968477628369</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73304327121221</v>
+        <v>4.734101601311697</v>
       </c>
       <c r="K17" t="n">
-        <v>18.53145003040871</v>
+        <v>17.58478998911168</v>
       </c>
       <c r="L17" t="n">
-        <v>43.83191903042079</v>
+        <v>43.8421457321718</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93805456327669</v>
+        <v>99.93471946667384</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.06285576015081</v>
+        <v>80.03295993662525</v>
       </c>
       <c r="C18" t="n">
-        <v>35.45588571494433</v>
+        <v>36.42827745103921</v>
       </c>
       <c r="D18" t="n">
-        <v>1.262194688232923</v>
+        <v>1.303594880860375</v>
       </c>
       <c r="E18" t="n">
-        <v>11.83506583069356</v>
+        <v>12.17003799732194</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577820659390353</v>
+        <v>0.7579718774502773</v>
       </c>
       <c r="G18" t="n">
-        <v>21.62402551570926</v>
+        <v>22.22147042260362</v>
       </c>
       <c r="H18" t="n">
-        <v>37.29682208571415</v>
+        <v>37.208141622736</v>
       </c>
       <c r="I18" t="n">
-        <v>1.550827661742902</v>
+        <v>1.634418901588815</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736137912118971</v>
+        <v>4.737324234064233</v>
       </c>
       <c r="K18" t="n">
-        <v>20.93714423984918</v>
+        <v>19.96704006337474</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55530956736977</v>
+        <v>43.55023891676304</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94833952216328</v>
+        <v>99.945556431177</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.12158551375008</v>
+        <v>79.08459165432282</v>
       </c>
       <c r="C19" t="n">
-        <v>34.74971601622175</v>
+        <v>35.73170952115446</v>
       </c>
       <c r="D19" t="n">
-        <v>1.228509974814146</v>
+        <v>1.269689110642232</v>
       </c>
       <c r="E19" t="n">
-        <v>11.73529112158604</v>
+        <v>12.08063516540826</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582012482767118</v>
+        <v>0.7584072604636061</v>
       </c>
       <c r="G19" t="n">
-        <v>21.04693617343295</v>
+        <v>21.64350246559477</v>
       </c>
       <c r="H19" t="n">
-        <v>37.31745357037514</v>
+        <v>37.22951417401661</v>
       </c>
       <c r="I19" t="n">
-        <v>1.29643562353565</v>
+        <v>1.362798100299818</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738757801729449</v>
+        <v>4.740045377897538</v>
       </c>
       <c r="K19" t="n">
-        <v>21.87841448624989</v>
+        <v>20.91540834567715</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32867886850592</v>
+        <v>43.30748160812425</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95680937097758</v>
+        <v>99.95459947495586</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.46689063408152</v>
+        <v>76.51607458813304</v>
       </c>
       <c r="C20" t="n">
-        <v>32.2943041417101</v>
+        <v>33.3729944498496</v>
       </c>
       <c r="D20" t="n">
-        <v>1.133159839549335</v>
+        <v>1.177077358095214</v>
       </c>
       <c r="E20" t="n">
-        <v>11.00460933472631</v>
+        <v>11.38883885676924</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585632276172635</v>
+        <v>0.758782660002257</v>
       </c>
       <c r="G20" t="n">
-        <v>19.41338963967342</v>
+        <v>20.06481467675443</v>
       </c>
       <c r="H20" t="n">
-        <v>37.33526961494798</v>
+        <v>37.24794219175023</v>
       </c>
       <c r="I20" t="n">
-        <v>1.080878804959326</v>
+        <v>1.136227219747567</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741020172607898</v>
+        <v>4.742391625014106</v>
       </c>
       <c r="K20" t="n">
-        <v>24.53310936591848</v>
+        <v>23.48392541186696</v>
       </c>
       <c r="L20" t="n">
-        <v>43.13657439171763</v>
+        <v>43.10522463549734</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96398789934621</v>
+        <v>99.9621444972139</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.3084367365057</v>
+        <v>82.22976768703313</v>
       </c>
       <c r="C21" t="n">
-        <v>36.01096844290389</v>
+        <v>36.94784795308204</v>
       </c>
       <c r="D21" t="n">
-        <v>1.133830440564298</v>
+        <v>1.177837480423491</v>
       </c>
       <c r="E21" t="n">
-        <v>12.98313552615466</v>
+        <v>13.30926355468075</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590121433417703</v>
+        <v>0.7592726597785763</v>
       </c>
       <c r="G21" t="n">
-        <v>21.15630152932643</v>
+        <v>21.72533410395852</v>
       </c>
       <c r="H21" t="n">
-        <v>39.08878762606946</v>
+        <v>38.91955798301564</v>
       </c>
       <c r="I21" t="n">
-        <v>1.443543575163014</v>
+        <v>1.593047781560052</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743825895886065</v>
+        <v>4.745454123616101</v>
       </c>
       <c r="K21" t="n">
-        <v>18.69156326349432</v>
+        <v>17.77023231296686</v>
       </c>
       <c r="L21" t="n">
-        <v>45.24937863376399</v>
+        <v>45.22885241056667</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95191034016219</v>
+        <v>99.94693267661557</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_88_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_88_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.25906449791488</v>
+        <v>43.33274158455439</v>
       </c>
       <c r="M2" t="n">
-        <v>100.022290745528</v>
+        <v>98.7400147524838</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98673777596514</v>
+        <v>81.54554412826087</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90305264062242</v>
+        <v>43.30109968381642</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228645944559007</v>
+        <v>2.184080985344408</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689514319665689</v>
+        <v>4.154038622475582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428819815196692</v>
+        <v>0.7376813880850872</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96464613358971</v>
+        <v>32.85221815455546</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17257114990478</v>
+        <v>33.93334385191401</v>
       </c>
       <c r="I3" t="n">
-        <v>6.545465862228343</v>
+        <v>3.07367245035453</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643012384497932</v>
+        <v>4.610508675531795</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01326222403485</v>
+        <v>18.45445587173913</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84872755033167</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.765042414989</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.01679290937517</v>
+        <v>88.62338899871345</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56483599360912</v>
+        <v>42.85241862726899</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18159210580652</v>
+        <v>2.189841586243035</v>
       </c>
       <c r="E4" t="n">
-        <v>6.48038646298469</v>
+        <v>6.509316415004144</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444374571287393</v>
+        <v>0.739627052231984</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24754390101798</v>
+        <v>33.52665854077093</v>
       </c>
       <c r="H4" t="n">
-        <v>34.244123027922</v>
+        <v>34.02284440267126</v>
       </c>
       <c r="I4" t="n">
-        <v>5.46597584746062</v>
+        <v>7.012431925342204</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65273410705462</v>
+        <v>4.622669076449901</v>
       </c>
       <c r="K4" t="n">
-        <v>12.98320709062486</v>
+        <v>11.37661100128654</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27013841959299</v>
+        <v>45.5378375377671</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81818150382696</v>
+        <v>99.76686716632263</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.86511992243439</v>
+        <v>87.56506864406023</v>
       </c>
       <c r="C5" t="n">
-        <v>42.26145025214448</v>
+        <v>42.88107211811662</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125400270905126</v>
+        <v>2.13971665444889</v>
       </c>
       <c r="E5" t="n">
-        <v>7.073977559823236</v>
+        <v>7.336440046044293</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457561549029267</v>
+        <v>0.7412760316043164</v>
       </c>
       <c r="G5" t="n">
-        <v>32.39117827116887</v>
+        <v>32.7592416265982</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30478312553462</v>
+        <v>34.09869745379855</v>
       </c>
       <c r="I5" t="n">
-        <v>4.563048571956312</v>
+        <v>5.856721634039023</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660975968143291</v>
+        <v>4.632975197526979</v>
       </c>
       <c r="K5" t="n">
-        <v>14.13488007756562</v>
+        <v>12.43493135593975</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45183700786047</v>
+        <v>44.48920675023967</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84816733757056</v>
+        <v>99.80521022429603</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.48550194050144</v>
+        <v>86.29878748092803</v>
       </c>
       <c r="C6" t="n">
-        <v>41.59045102097226</v>
+        <v>42.52382675584668</v>
       </c>
       <c r="D6" t="n">
-        <v>2.057985257272667</v>
+        <v>2.079484865002747</v>
       </c>
       <c r="E6" t="n">
-        <v>7.484308904427374</v>
+        <v>7.944893397073749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468766740922376</v>
+        <v>0.7426760921971646</v>
       </c>
       <c r="G6" t="n">
-        <v>31.36377098482637</v>
+        <v>31.83708787321874</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35632700824292</v>
+        <v>34.16310024106956</v>
       </c>
       <c r="I6" t="n">
-        <v>3.808253898563398</v>
+        <v>4.88981943613379</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667979213076484</v>
+        <v>4.64172557623228</v>
       </c>
       <c r="K6" t="n">
-        <v>15.51449805949855</v>
+        <v>13.70121251907197</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76829957030817</v>
+        <v>43.61227401302472</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87324865077898</v>
+        <v>99.83731328794337</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.83125322206455</v>
+        <v>84.85850085002893</v>
       </c>
       <c r="C7" t="n">
-        <v>40.52761725476002</v>
+        <v>41.84299718494522</v>
       </c>
       <c r="D7" t="n">
-        <v>1.977285174616775</v>
+        <v>2.011157206031568</v>
       </c>
       <c r="E7" t="n">
-        <v>7.720426095772588</v>
+        <v>8.364070694501873</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478317393692447</v>
+        <v>0.7438667586523406</v>
       </c>
       <c r="G7" t="n">
-        <v>30.13389875812722</v>
+        <v>30.7909856776955</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40026001098525</v>
+        <v>34.21787089800767</v>
       </c>
       <c r="I7" t="n">
-        <v>3.177603072135687</v>
+        <v>4.081382373562854</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673948371057779</v>
+        <v>4.64916724157713</v>
       </c>
       <c r="K7" t="n">
-        <v>17.16874677793543</v>
+        <v>15.14149914997106</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19785113678891</v>
+        <v>42.87967534741334</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89421516948437</v>
+        <v>99.86417168232963</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.80202852384625</v>
+        <v>83.20913273975037</v>
       </c>
       <c r="C8" t="n">
-        <v>42.86634089345949</v>
+        <v>40.82757088959755</v>
       </c>
       <c r="D8" t="n">
-        <v>1.981552409529754</v>
+        <v>1.933212039427352</v>
       </c>
       <c r="E8" t="n">
-        <v>9.580790854146526</v>
+        <v>8.607541675395106</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494456561417144</v>
+        <v>0.744881653542634</v>
       </c>
       <c r="G8" t="n">
-        <v>30.64706303314896</v>
+        <v>29.5976386328408</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47450018251886</v>
+        <v>34.26455606296116</v>
       </c>
       <c r="I8" t="n">
-        <v>5.684641037474714</v>
+        <v>3.405792340941852</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684035350885715</v>
+        <v>4.655510334641463</v>
       </c>
       <c r="K8" t="n">
-        <v>12.19797147615376</v>
+        <v>16.79086726024963</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74660765463371</v>
+        <v>42.26819011755384</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81092002424695</v>
+        <v>99.88662826740102</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.79586632378928</v>
+        <v>81.27121050351738</v>
       </c>
       <c r="C9" t="n">
-        <v>41.74222323033705</v>
+        <v>39.41837847899261</v>
       </c>
       <c r="D9" t="n">
-        <v>1.890851711591879</v>
+        <v>1.842018842208926</v>
       </c>
       <c r="E9" t="n">
-        <v>9.933242956019249</v>
+        <v>8.675085962840393</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508275490256746</v>
+        <v>0.7457497581405319</v>
       </c>
       <c r="G9" t="n">
-        <v>29.24426894428996</v>
+        <v>28.20146312700033</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53806725518103</v>
+        <v>34.30448887446447</v>
       </c>
       <c r="I9" t="n">
-        <v>4.745935726271021</v>
+        <v>2.841467950484398</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692672181410466</v>
+        <v>4.660935988378325</v>
       </c>
       <c r="K9" t="n">
-        <v>14.20413367621072</v>
+        <v>18.72878949648261</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89573639796684</v>
+        <v>41.75822668172083</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84209330451461</v>
+        <v>99.90539465719607</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.69839117098132</v>
+        <v>85.91217569846135</v>
       </c>
       <c r="C10" t="n">
-        <v>40.38087374787868</v>
+        <v>42.61202306780648</v>
       </c>
       <c r="D10" t="n">
-        <v>1.797111265649347</v>
+        <v>1.844098209581919</v>
       </c>
       <c r="E10" t="n">
-        <v>10.10099230470523</v>
+        <v>10.50296360277467</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520120271049393</v>
+        <v>0.7465915995375695</v>
       </c>
       <c r="G10" t="n">
-        <v>27.79446153988321</v>
+        <v>29.56647234000764</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5925532468272</v>
+        <v>35.67638750267484</v>
       </c>
       <c r="I10" t="n">
-        <v>3.961185617405537</v>
+        <v>2.909464946774924</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700075169405871</v>
+        <v>4.66619749710981</v>
       </c>
       <c r="K10" t="n">
-        <v>16.30160882901866</v>
+        <v>14.08782430153862</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18568587515067</v>
+        <v>43.20327982086528</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86816845204801</v>
+        <v>99.90312719021037</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.45097777008448</v>
+        <v>85.60377929212633</v>
       </c>
       <c r="C11" t="n">
-        <v>38.74732840552995</v>
+        <v>42.68081126594251</v>
       </c>
       <c r="D11" t="n">
-        <v>1.697651277727326</v>
+        <v>1.82628844190063</v>
       </c>
       <c r="E11" t="n">
-        <v>10.09286816287799</v>
+        <v>10.84059648364615</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753029301858441</v>
+        <v>0.7473107193929666</v>
       </c>
       <c r="G11" t="n">
-        <v>26.25619462124754</v>
+        <v>29.30772594001091</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63934788548828</v>
+        <v>35.73754918123118</v>
       </c>
       <c r="I11" t="n">
-        <v>3.305453384269636</v>
+        <v>2.473616529738438</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706433136615257</v>
+        <v>4.670691996206042</v>
       </c>
       <c r="K11" t="n">
-        <v>18.54902222991554</v>
+        <v>14.39622070787368</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59361643073768</v>
+        <v>42.84059348532882</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88996706618316</v>
+        <v>99.91762545914501</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.14553095628763</v>
+        <v>83.74709803385475</v>
       </c>
       <c r="C12" t="n">
-        <v>36.95338729772971</v>
+        <v>41.20879817803165</v>
       </c>
       <c r="D12" t="n">
-        <v>1.596634106869513</v>
+        <v>1.746938731451464</v>
       </c>
       <c r="E12" t="n">
-        <v>9.95192533324801</v>
+        <v>10.71342749879818</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539039193129358</v>
+        <v>0.7479243652241014</v>
       </c>
       <c r="G12" t="n">
-        <v>24.69384401784135</v>
+        <v>28.034345725852</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67958028839504</v>
+        <v>35.76689466966182</v>
       </c>
       <c r="I12" t="n">
-        <v>2.757743794914931</v>
+        <v>2.063039760216548</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711899495705849</v>
+        <v>4.674527282650635</v>
       </c>
       <c r="K12" t="n">
-        <v>20.85446904371237</v>
+        <v>16.25290196614525</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1003255089949</v>
+        <v>42.46958828555259</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90818185043697</v>
+        <v>99.93128842972949</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.91311236069588</v>
+        <v>84.88516942504879</v>
       </c>
       <c r="C13" t="n">
-        <v>35.14690875319604</v>
+        <v>42.16504215524257</v>
       </c>
       <c r="D13" t="n">
-        <v>1.499780196671745</v>
+        <v>1.748252147697056</v>
       </c>
       <c r="E13" t="n">
-        <v>9.731630377311857</v>
+        <v>11.3425818368201</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546555418523776</v>
+        <v>0.7484866837496876</v>
       </c>
       <c r="G13" t="n">
-        <v>23.19588318846196</v>
+        <v>28.3574227998871</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71415492520936</v>
+        <v>36.09578537368851</v>
       </c>
       <c r="I13" t="n">
-        <v>2.300410994611218</v>
+        <v>1.914598809770775</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71659713657736</v>
+        <v>4.678041773435548</v>
       </c>
       <c r="K13" t="n">
-        <v>23.0868876393041</v>
+        <v>15.11483057495121</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68959961319666</v>
+        <v>42.65635525575234</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92339600569682</v>
+        <v>99.93622798594612</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.62462500774997</v>
+        <v>82.97488474212534</v>
       </c>
       <c r="C14" t="n">
-        <v>39.38496107538261</v>
+        <v>40.55237528658755</v>
       </c>
       <c r="D14" t="n">
-        <v>1.501485868948057</v>
+        <v>1.668747562543448</v>
       </c>
       <c r="E14" t="n">
-        <v>12.08435571790041</v>
+        <v>11.09284669156022</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555137976412986</v>
+        <v>0.7489667389265454</v>
       </c>
       <c r="G14" t="n">
-        <v>25.08839747862212</v>
+        <v>27.06782327690047</v>
       </c>
       <c r="H14" t="n">
-        <v>36.61976873276281</v>
+        <v>36.11893604424498</v>
       </c>
       <c r="I14" t="n">
-        <v>2.853142176617161</v>
+        <v>1.596522309658771</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721961235258116</v>
+        <v>4.681042118290909</v>
       </c>
       <c r="K14" t="n">
-        <v>16.37537499225003</v>
+        <v>17.02511525787466</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14466723113793</v>
+        <v>42.36932615526637</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90500329877057</v>
+        <v>99.94681669972857</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.00616322398264</v>
+        <v>82.12172635218079</v>
       </c>
       <c r="C15" t="n">
-        <v>39.20756082609695</v>
+        <v>39.9258048814344</v>
       </c>
       <c r="D15" t="n">
-        <v>1.478886788379759</v>
+        <v>1.63286828890413</v>
       </c>
       <c r="E15" t="n">
-        <v>12.29912080059524</v>
+        <v>11.07961817746232</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562358485747722</v>
+        <v>0.7493776508596331</v>
       </c>
       <c r="G15" t="n">
-        <v>24.71078838640597</v>
+        <v>26.48584559497213</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65476655580672</v>
+        <v>36.13875228048035</v>
       </c>
       <c r="I15" t="n">
-        <v>2.379890790627841</v>
+        <v>1.351654041629512</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726474053592327</v>
+        <v>4.683610317872708</v>
       </c>
       <c r="K15" t="n">
-        <v>16.99383677601735</v>
+        <v>17.87827364781922</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71934844853522</v>
+        <v>42.15089104144928</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92074605064954</v>
+        <v>99.9549695707029</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.64436295439906</v>
+        <v>79.76965520234629</v>
       </c>
       <c r="C16" t="n">
-        <v>37.21377194195935</v>
+        <v>37.7833682903678</v>
       </c>
       <c r="D16" t="n">
-        <v>1.38927624326295</v>
+        <v>1.535611839968021</v>
       </c>
       <c r="E16" t="n">
-        <v>11.88468876685721</v>
+        <v>10.6075151573162</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568562802058053</v>
+        <v>0.7497305336916055</v>
       </c>
       <c r="G16" t="n">
-        <v>23.21348160473003</v>
+        <v>24.90830299270513</v>
       </c>
       <c r="H16" t="n">
-        <v>36.68483888924901</v>
+        <v>36.15577006214765</v>
       </c>
       <c r="I16" t="n">
-        <v>1.984869418807759</v>
+        <v>1.126908780945135</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730351751286283</v>
+        <v>4.685815835572535</v>
       </c>
       <c r="K16" t="n">
-        <v>19.35563704560095</v>
+        <v>20.23034479765373</v>
       </c>
       <c r="L16" t="n">
-        <v>43.36448293492224</v>
+        <v>41.94874096637766</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93389192248254</v>
+        <v>99.96245405439919</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.41521001088832</v>
+        <v>84.31496054094519</v>
       </c>
       <c r="C17" t="n">
-        <v>38.50778374539037</v>
+        <v>40.77021699853373</v>
       </c>
       <c r="D17" t="n">
-        <v>1.39037755196683</v>
+        <v>1.53639099504702</v>
       </c>
       <c r="E17" t="n">
-        <v>12.6896819370207</v>
+        <v>12.20513033954163</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574562562098716</v>
+        <v>0.7501109399492303</v>
       </c>
       <c r="G17" t="n">
-        <v>23.70079393598982</v>
+        <v>26.29927115061715</v>
       </c>
       <c r="H17" t="n">
-        <v>37.18283025076104</v>
+        <v>37.55244507960903</v>
       </c>
       <c r="I17" t="n">
-        <v>1.959968477628369</v>
+        <v>1.283418661498446</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734101601311697</v>
+        <v>4.688193374682689</v>
       </c>
       <c r="K17" t="n">
-        <v>17.58478998911168</v>
+        <v>15.6850394590548</v>
       </c>
       <c r="L17" t="n">
-        <v>43.8421457321718</v>
+        <v>43.50198461584078</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93471946667384</v>
+        <v>99.9572410734293</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.03295993662525</v>
+        <v>85.83688546702268</v>
       </c>
       <c r="C18" t="n">
-        <v>36.42827745103921</v>
+        <v>41.48918777596936</v>
       </c>
       <c r="D18" t="n">
-        <v>1.303594880860375</v>
+        <v>1.537608545269092</v>
       </c>
       <c r="E18" t="n">
-        <v>12.17003799732194</v>
+        <v>12.79406693417765</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579718774502773</v>
+        <v>0.750705383515001</v>
       </c>
       <c r="G18" t="n">
-        <v>22.22147042260362</v>
+        <v>26.4396860238284</v>
       </c>
       <c r="H18" t="n">
-        <v>37.208141622736</v>
+        <v>37.58220442341761</v>
       </c>
       <c r="I18" t="n">
-        <v>1.634418901588815</v>
+        <v>2.040705509846166</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737324234064233</v>
+        <v>4.691908646968757</v>
       </c>
       <c r="K18" t="n">
-        <v>19.96704006337474</v>
+        <v>14.16311453297731</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55023891676304</v>
+        <v>44.27972803825458</v>
       </c>
       <c r="M18" t="n">
-        <v>99.945556431177</v>
+        <v>99.93203034720125</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.08459165432282</v>
+        <v>83.14549285816936</v>
       </c>
       <c r="C19" t="n">
-        <v>35.73170952115446</v>
+        <v>39.11410559874878</v>
       </c>
       <c r="D19" t="n">
-        <v>1.269689110642232</v>
+        <v>1.437087941602963</v>
       </c>
       <c r="E19" t="n">
-        <v>12.08063516540826</v>
+        <v>12.24128411438295</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584072604636061</v>
+        <v>0.7512175425581078</v>
       </c>
       <c r="G19" t="n">
-        <v>21.64350246559477</v>
+        <v>24.71120109309917</v>
       </c>
       <c r="H19" t="n">
-        <v>37.22951417401661</v>
+        <v>37.60784439653892</v>
       </c>
       <c r="I19" t="n">
-        <v>1.362798100299818</v>
+        <v>1.701748128999079</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740045377897538</v>
+        <v>4.695109640988173</v>
       </c>
       <c r="K19" t="n">
-        <v>20.91540834567715</v>
+        <v>16.85450714183065</v>
       </c>
       <c r="L19" t="n">
-        <v>43.30748160812425</v>
+        <v>43.97470099525817</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95459947495586</v>
+        <v>99.94331373583761</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.51607458813304</v>
+        <v>80.34482191235631</v>
       </c>
       <c r="C20" t="n">
-        <v>33.3729944498496</v>
+        <v>36.57647365263556</v>
       </c>
       <c r="D20" t="n">
-        <v>1.177077358095214</v>
+        <v>1.333030989008252</v>
       </c>
       <c r="E20" t="n">
-        <v>11.38883885676924</v>
+        <v>11.5914078003929</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758782660002257</v>
+        <v>0.7516597807049592</v>
       </c>
       <c r="G20" t="n">
-        <v>20.06481467675443</v>
+        <v>22.92190747629042</v>
       </c>
       <c r="H20" t="n">
-        <v>37.24794219175023</v>
+        <v>37.62998395328618</v>
       </c>
       <c r="I20" t="n">
-        <v>1.136227219747567</v>
+        <v>1.418958283267615</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742391625014106</v>
+        <v>4.697873629405994</v>
       </c>
       <c r="K20" t="n">
-        <v>23.48392541186696</v>
+        <v>19.65517808764369</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10522463549734</v>
+        <v>43.72107747835965</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9621444972139</v>
+        <v>99.95272921863891</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.22976768703313</v>
+        <v>77.59843179711106</v>
       </c>
       <c r="C21" t="n">
-        <v>36.94784795308204</v>
+        <v>34.04869347049401</v>
       </c>
       <c r="D21" t="n">
-        <v>1.177837480423491</v>
+        <v>1.231525534278161</v>
       </c>
       <c r="E21" t="n">
-        <v>13.30926355468075</v>
+        <v>10.90594200808873</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592726597785763</v>
+        <v>0.7520417743585449</v>
       </c>
       <c r="G21" t="n">
-        <v>21.72533410395852</v>
+        <v>21.17648770672231</v>
       </c>
       <c r="H21" t="n">
-        <v>38.91955798301564</v>
+        <v>37.64910751879238</v>
       </c>
       <c r="I21" t="n">
-        <v>1.593047781560052</v>
+        <v>1.183066165130049</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745454123616101</v>
+        <v>4.700261089740906</v>
       </c>
       <c r="K21" t="n">
-        <v>17.77023231296686</v>
+        <v>22.40156820288893</v>
       </c>
       <c r="L21" t="n">
-        <v>45.22885241056667</v>
+        <v>43.51032281874852</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94693267661557</v>
+        <v>99.96058449213146</v>
       </c>
     </row>
   </sheetData>
